--- a/config/trg_mc_2025a/trg_mc_2025a_tuples.xlsx
+++ b/config/trg_mc_2025a/trg_mc_2025a_tuples.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schellma/Dropbox/prod/merge-utils/config/trg_mc_2025a/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4399177-332A-7E4E-AA6D-FF812DC2A4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CA4B26-F3B3-7443-9AC4-5A068C20511F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMPLETE" sheetId="1" r:id="rId1"/>
-    <sheet name="trg_mc_2025a" sheetId="2" r:id="rId2"/>
-    <sheet name="LATERAL" sheetId="3" r:id="rId3"/>
-    <sheet name="current" sheetId="4" r:id="rId4"/>
+    <sheet name="official set" sheetId="6" r:id="rId2"/>
+    <sheet name="trg_mc_2025a" sheetId="2" r:id="rId3"/>
+    <sheet name="LATERAL" sheetId="3" r:id="rId4"/>
+    <sheet name="current" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="123">
   <si>
     <t>TASK</t>
   </si>
@@ -386,6 +387,39 @@
   </si>
   <si>
     <t>files where merge.tag=NU_prod-pass2_v2 and core.run_type='fardet-hd' and dune.output_status=confirmed and core.data_tier='root-tuple' and dune.campaign=trg_mc_2025a_tpg and merge.dataset='fardet-hd:fardet-hd__trg_mc_2025a_tpg__trigger-primitives__v10_12_01d01__tpg_dune10kt_1x2x6__prodgenie_nu_dune10kt_1x2x6__out1__v1_official' and merge.cfg='triggerana_dune10kt_1x2x6.fcl'</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prod_eminus_1-500MeV_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prod_muminus_1-500MeV_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prod_p_1-500MeV_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prodgenie_nue_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x2__prodmarley_nue_flat_cc_dune10kt_1x2x2__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prod_gamma_1-500MeV_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prodbackground_radiological_decay0_dune10kt_1x2x6_centralAPA__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prodgenie_nu_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prodbackground_radiological_decay0_dune10kt_1x2x6_lateralAPA__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x6__prodbackground_radiological_decay0_cavernneutrons_dune10kt_1x2x6__out1__v1_official</t>
+  </si>
+  <si>
+    <t>fardet-hd:fardet-hd__trg_mc_2025a_tpg__root-tuple__v10_12_01d01__triggerana_dune10kt_1x2x2__prodmarley_nue_flat_es_dune10kt_1x2x2__out1__v1_official</t>
   </si>
 </sst>
 </file>
@@ -29012,6 +29046,71 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD41B6AE-0BB3-E244-B097-9FB992BF5A13}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34042,7 +34141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34250,7 +34349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
